--- a/config-source/showcase/localization-default.xlsx
+++ b/config-source/showcase/localization-default.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="114">
   <si>
     <t>formatVersion</t>
   </si>
@@ -203,6 +203,135 @@
     <t>Preparation cancelled.</t>
   </si>
   <si>
+    <t>example.title</t>
+  </si>
+  <si>
+    <t>示例页标题</t>
+  </si>
+  <si>
+    <t>多语言示例</t>
+  </si>
+  <si>
+    <t>Localization examples</t>
+  </si>
+  <si>
+    <t>example.subtitle</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>代码动态绑定 · 编辑器固定配置</t>
+  </si>
+  <si>
+    <t>Code bindings · Inspector bindings</t>
+  </si>
+  <si>
+    <t>example.dynamicText</t>
+  </si>
+  <si>
+    <t>动态文字卡</t>
+  </si>
+  <si>
+    <t>01  动态文字</t>
+  </si>
+  <si>
+    <t>01  Dynamic text</t>
+  </si>
+  <si>
+    <t>example.counter</t>
+  </si>
+  <si>
+    <t>动态参数</t>
+  </si>
+  <si>
+    <t>你已点击 {count} 次</t>
+  </si>
+  <si>
+    <t>You clicked {count} times</t>
+  </si>
+  <si>
+    <t>example.increment</t>
+  </si>
+  <si>
+    <t>按钮</t>
+  </si>
+  <si>
+    <t>点击 +1</t>
+  </si>
+  <si>
+    <t>Click +1</t>
+  </si>
+  <si>
+    <t>example.dynamicImage</t>
+  </si>
+  <si>
+    <t>动态图片卡</t>
+  </si>
+  <si>
+    <t>02  动态图片加载</t>
+  </si>
+  <si>
+    <t>02  Dynamic image</t>
+  </si>
+  <si>
+    <t>example.load</t>
+  </si>
+  <si>
+    <t>加载 / 重新绑定图片</t>
+  </si>
+  <si>
+    <t>Load / rebind image</t>
+  </si>
+  <si>
+    <t>example.staticText</t>
+  </si>
+  <si>
+    <t>固定文字卡</t>
+  </si>
+  <si>
+    <t>03  编辑器配置的文字</t>
+  </si>
+  <si>
+    <t>03  Inspector text</t>
+  </si>
+  <si>
+    <t>example.welcome</t>
+  </si>
+  <si>
+    <t>由原生 LocalizedLabel 绑定</t>
+  </si>
+  <si>
+    <t>欢迎，{name}！</t>
+  </si>
+  <si>
+    <t>Welcome, {name}!</t>
+  </si>
+  <si>
+    <t>example.staticImage</t>
+  </si>
+  <si>
+    <t>固定图片卡</t>
+  </si>
+  <si>
+    <t>04  编辑器配置的图片</t>
+  </si>
+  <si>
+    <t>04  Inspector image</t>
+  </si>
+  <si>
+    <t>example.help</t>
+  </si>
+  <si>
+    <t>页尾提示</t>
+  </si>
+  <si>
+    <t>前两项查看页面脚本；后两项查看节点上的文字绑定 / 图片绑定组件。</t>
+  </si>
+  <si>
+    <t>See the page script for the first two; inspect the binding components for the last two.</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -219,6 +348,18 @@
   </si>
   <si>
     <t>c4a26f30-0d8d-43fb-a616-9051ca96cbb7@f9941</t>
+  </si>
+  <si>
+    <t>example.greeting</t>
+  </si>
+  <si>
+    <t>动态与编辑器配置共用此语言键</t>
+  </si>
+  <si>
+    <t>d3246fa4-a314-4e26-b918-74bdf89848c1@f9941</t>
+  </si>
+  <si>
+    <t>9505d170-d74f-48b5-a438-02d586d11077@f9941</t>
   </si>
 </sst>
 </file>
@@ -660,7 +801,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="32" customWidth="1"/>
@@ -722,7 +863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -913,6 +1054,160 @@
       </c>
       <c r="D18" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="32" customWidth="1"/>
@@ -934,7 +1229,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -948,19 +1243,36 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/config-source/showcase/localization-default.xlsx
+++ b/config-source/showcase/localization-default.xlsx
@@ -7,14 +7,13 @@
     <sheet sheetId="1" name="__localization" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="__help" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="texts" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="assets" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="104">
   <si>
     <t>formatVersion</t>
   </si>
@@ -22,16 +21,16 @@
     <t>空单元格表示缺译；#EMPTY 表示有意留空；##EMPTY 输出字面 #EMPTY。</t>
   </si>
   <si>
-    <t>保留空格和换行，禁止公式或数字值。参数使用 {name}，两种语言参数必须一致。</t>
-  </si>
-  <si>
-    <t>资源填写 Creator UUID（精灵帧含 @ 子资源 ID），或 @模块/包/类型/逻辑路径。</t>
-  </si>
-  <si>
-    <t>assets 页 $font / Font 为该语言字体；文案回退时使用默认语言的字体。</t>
-  </si>
-  <si>
-    <t>工作簿归属和存放位置由模块资源包声明统一管理。新增语言须在 texts 和 assets 页添加同名列。</t>
+    <t>保留空格和换行，禁止公式或数字值。参数使用 {name}，各语言参数必须一致。</t>
+  </si>
+  <si>
+    <t>资源放入各语言 dynamic 下相同相对路径，key 不含扩展名，例如 images/greeting。</t>
+  </si>
+  <si>
+    <t>dynamic/fonts/default 为可选默认字体；改名会改变 key，需要同步修改组件与代码。</t>
+  </si>
+  <si>
+    <t>这里只维护 texts 文案页，资源不需要填写 UUID 或配置表。</t>
   </si>
   <si>
     <t>key</t>
@@ -330,36 +329,6 @@
   </si>
   <si>
     <t>See the page script for the first two; inspect the binding components for the last two.</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>resources.logo</t>
-  </si>
-  <si>
-    <t>SpriteFrame</t>
-  </si>
-  <si>
-    <t>不同语言使用不同图片</t>
-  </si>
-  <si>
-    <t>003008bf-7ef9-4c8a-b839-927a2675d16a@f9941</t>
-  </si>
-  <si>
-    <t>c4a26f30-0d8d-43fb-a616-9051ca96cbb7@f9941</t>
-  </si>
-  <si>
-    <t>example.greeting</t>
-  </si>
-  <si>
-    <t>动态与编辑器配置共用此语言键</t>
-  </si>
-  <si>
-    <t>d3246fa4-a314-4e26-b918-74bdf89848c1@f9941</t>
-  </si>
-  <si>
-    <t>9505d170-d74f-48b5-a438-02d586d11077@f9941</t>
   </si>
 </sst>
 </file>
@@ -751,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -768,8 +737,8 @@
     <col min="1" max="1" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1214,69 +1183,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="5" width="32" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
 </file>